--- a/investigacion/Bases/bruto/saldo-caja-tesoro.xlsx
+++ b/investigacion/Bases/bruto/saldo-caja-tesoro.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/31aa1ff112bd5f3a/Desktop/GitHub/deuda-publica/investigacion/Bases/bruto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{4B2D8B45-F07E-4910-9510-2BBBAEE14AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0622C148-140B-4D8E-8DB8-D76B232BAC3F}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="8_{4B2D8B45-F07E-4910-9510-2BBBAEE14AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEB31402-F719-4FCB-8244-495D2AE2427F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{2D8852EA-F075-4C4B-A4C1-A0C97F97AC06}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{2D8852EA-F075-4C4B-A4C1-A0C97F97AC06}"/>
   </bookViews>
   <sheets>
-    <sheet name="hoja-bruta" sheetId="1" r:id="rId1"/>
+    <sheet name="hoja-bruta-tesoro" sheetId="1" r:id="rId1"/>
     <sheet name="export-csv" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -215,6 +215,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
